--- a/ProducaoIndustrial2026_estendida.xlsx
+++ b/ProducaoIndustrial2026_estendida.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wkuba\Projetos\analisador_producao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8CA75-9875-4D33-B20A-3B66D62041C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -22,12 +28,6 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Terminal MP35</t>
-  </si>
-  <si>
-    <t>Terminal MP30</t>
-  </si>
-  <si>
     <t>Ana Silva</t>
   </si>
   <si>
@@ -197,13 +197,19 @@
   </si>
   <si>
     <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>Terminal MP1</t>
+  </si>
+  <si>
+    <t>Terminal MP1S</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,13 +246,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -284,7 +298,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -318,6 +332,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -352,9 +367,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,11 +543,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X186"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,75 +558,75 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" t="s">
-        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -631,9 +650,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -657,9 +676,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -683,9 +702,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -709,9 +728,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -735,9 +754,9 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -761,9 +780,9 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -787,9 +806,9 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -813,9 +832,9 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -839,9 +858,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -865,9 +884,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -891,9 +910,9 @@
         <v>692</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -917,9 +936,9 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -943,9 +962,9 @@
         <v>784</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -969,9 +988,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -995,9 +1014,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1021,9 +1040,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1047,9 +1066,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -1073,9 +1092,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1099,9 +1118,9 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -1125,9 +1144,9 @@
         <v>870</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1151,9 +1170,9 @@
         <v>445</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1177,9 +1196,9 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -1203,9 +1222,9 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1229,9 +1248,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -1255,9 +1274,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1281,9 +1300,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1307,9 +1326,9 @@
         <v>559</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -1333,9 +1352,9 @@
         <v>490</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1359,9 +1378,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -1385,9 +1404,9 @@
         <v>492</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1411,9 +1430,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1437,9 +1456,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -1463,9 +1482,9 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -1489,9 +1508,9 @@
         <v>574</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>5</v>
@@ -1515,9 +1534,9 @@
         <v>684</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1541,9 +1560,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -1567,9 +1586,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -1593,9 +1612,9 @@
         <v>595</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1619,9 +1638,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -1645,9 +1664,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1671,9 +1690,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -1697,9 +1716,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -1723,9 +1742,9 @@
         <v>545</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -1749,9 +1768,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>5</v>
@@ -1775,9 +1794,9 @@
         <v>845</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -1801,9 +1820,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -1827,9 +1846,9 @@
         <v>786</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -1853,9 +1872,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B50">
         <v>4</v>
@@ -1879,9 +1898,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -1905,9 +1924,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1931,9 +1950,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1957,9 +1976,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>3</v>
@@ -1983,9 +2002,9 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -2009,9 +2028,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B56">
         <v>5</v>
@@ -2035,9 +2054,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2061,9 +2080,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -2087,9 +2106,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B59">
         <v>3</v>
@@ -2113,9 +2132,9 @@
         <v>692</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -2139,9 +2158,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -2165,9 +2184,9 @@
         <v>458</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -2191,9 +2210,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2217,9 +2236,9 @@
         <v>353</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -2243,9 +2262,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -2269,9 +2288,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -2295,9 +2314,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2321,9 +2340,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -2347,9 +2366,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -2373,9 +2392,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B70">
         <v>4</v>
@@ -2399,9 +2418,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -2425,9 +2444,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -2451,9 +2470,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -2477,9 +2496,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -2503,9 +2522,9 @@
         <v>877</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B75">
         <v>4</v>
@@ -2529,9 +2548,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -2555,9 +2574,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -2581,9 +2600,9 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -2607,9 +2626,9 @@
         <v>620</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -2633,9 +2652,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B80">
         <v>4</v>
@@ -2659,9 +2678,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -2685,9 +2704,9 @@
         <v>896</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -2711,9 +2730,9 @@
         <v>227</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -2737,9 +2756,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -2763,9 +2782,9 @@
         <v>973</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B85">
         <v>4</v>
@@ -2789,9 +2808,9 @@
         <v>423</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -2815,9 +2834,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -2841,9 +2860,9 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -2867,9 +2886,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -2893,9 +2912,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B90">
         <v>4</v>
@@ -2919,9 +2938,9 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -2945,9 +2964,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -2971,9 +2990,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -2997,9 +3016,9 @@
         <v>985</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -3023,9 +3042,9 @@
         <v>682</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B95">
         <v>4</v>
@@ -3049,9 +3068,9 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -3075,9 +3094,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -3101,9 +3120,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -3127,9 +3146,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -3153,9 +3172,9 @@
         <v>960</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B100">
         <v>4</v>
@@ -3179,9 +3198,9 @@
         <v>891</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B101">
         <v>5</v>
@@ -3205,9 +3224,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -3231,9 +3250,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B103">
         <v>2</v>
@@ -3257,9 +3276,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -3283,9 +3302,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B105">
         <v>4</v>
@@ -3309,9 +3328,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B106">
         <v>5</v>
@@ -3335,9 +3354,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -3361,9 +3380,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -3387,9 +3406,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -3413,9 +3432,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B110">
         <v>4</v>
@@ -3439,9 +3458,9 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -3465,9 +3484,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -3491,9 +3510,9 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -3517,9 +3536,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B114">
         <v>3</v>
@@ -3543,9 +3562,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -3569,9 +3588,9 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B116">
         <v>5</v>
@@ -3595,9 +3614,9 @@
         <v>476</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -3621,9 +3640,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -3647,9 +3666,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B119">
         <v>3</v>
@@ -3673,9 +3692,9 @@
         <v>435</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B120">
         <v>4</v>
@@ -3699,9 +3718,9 @@
         <v>583</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B121">
         <v>5</v>
@@ -3725,9 +3744,9 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -3751,9 +3770,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -3777,9 +3796,9 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B124">
         <v>3</v>
@@ -3803,9 +3822,9 @@
         <v>669</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B125">
         <v>4</v>
@@ -3829,9 +3848,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B126">
         <v>5</v>
@@ -3855,9 +3874,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -3881,9 +3900,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B128">
         <v>2</v>
@@ -3907,9 +3926,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B129">
         <v>3</v>
@@ -3933,9 +3952,9 @@
         <v>537</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B130">
         <v>4</v>
@@ -3959,9 +3978,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B131">
         <v>5</v>
@@ -3985,9 +4004,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -4011,9 +4030,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B133">
         <v>2</v>
@@ -4037,9 +4056,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B134">
         <v>3</v>
@@ -4063,9 +4082,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B135">
         <v>4</v>
@@ -4089,9 +4108,9 @@
         <v>833</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B136">
         <v>5</v>
@@ -4115,9 +4134,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -4141,9 +4160,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -4167,9 +4186,9 @@
         <v>601</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B139">
         <v>3</v>
@@ -4193,9 +4212,9 @@
         <v>528</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B140">
         <v>4</v>
@@ -4219,9 +4238,9 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B141">
         <v>5</v>
@@ -4245,9 +4264,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -4271,9 +4290,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B143">
         <v>2</v>
@@ -4297,9 +4316,9 @@
         <v>796</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B144">
         <v>3</v>
@@ -4323,9 +4342,9 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B145">
         <v>4</v>
@@ -4349,9 +4368,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B146">
         <v>5</v>
@@ -4375,9 +4394,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -4401,9 +4420,9 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B148">
         <v>2</v>
@@ -4427,9 +4446,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="149" spans="1:24">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B149">
         <v>3</v>
@@ -4453,9 +4472,9 @@
         <v>629</v>
       </c>
     </row>
-    <row r="150" spans="1:24">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B150">
         <v>4</v>
@@ -4479,9 +4498,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -4505,9 +4524,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -4531,9 +4550,9 @@
         <v>524</v>
       </c>
     </row>
-    <row r="153" spans="1:24">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B153">
         <v>2</v>
@@ -4557,9 +4576,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="154" spans="1:24">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B154">
         <v>3</v>
@@ -4583,9 +4602,9 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B155">
         <v>4</v>
@@ -4609,9 +4628,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -4635,9 +4654,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -4661,9 +4680,9 @@
         <v>326</v>
       </c>
     </row>
-    <row r="158" spans="1:24">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B158">
         <v>2</v>
@@ -4687,9 +4706,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="159" spans="1:24">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -4713,9 +4732,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="160" spans="1:24">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B160">
         <v>4</v>
@@ -4739,9 +4758,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="161" spans="1:24">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B161">
         <v>5</v>
@@ -4765,9 +4784,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="162" spans="1:24">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -4791,9 +4810,9 @@
         <v>627</v>
       </c>
     </row>
-    <row r="163" spans="1:24">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B163">
         <v>2</v>
@@ -4817,9 +4836,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:24">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B164">
         <v>3</v>
@@ -4843,9 +4862,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="165" spans="1:24">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B165">
         <v>4</v>
@@ -4869,9 +4888,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="166" spans="1:24">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B166">
         <v>5</v>
@@ -4895,9 +4914,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="167" spans="1:24">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -4921,9 +4940,9 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="168" spans="1:24">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B168">
         <v>2</v>
@@ -4947,9 +4966,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="1:24">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B169">
         <v>3</v>
@@ -4973,9 +4992,9 @@
         <v>397</v>
       </c>
     </row>
-    <row r="170" spans="1:24">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B170">
         <v>4</v>
@@ -4999,9 +5018,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:24">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B171">
         <v>5</v>
@@ -5025,9 +5044,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="172" spans="1:24">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -5051,9 +5070,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="173" spans="1:24">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B173">
         <v>2</v>
@@ -5077,9 +5096,9 @@
         <v>995</v>
       </c>
     </row>
-    <row r="174" spans="1:24">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B174">
         <v>3</v>
@@ -5103,9 +5122,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:24">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B175">
         <v>4</v>
@@ -5129,9 +5148,9 @@
         <v>296</v>
       </c>
     </row>
-    <row r="176" spans="1:24">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B176">
         <v>5</v>
@@ -5155,9 +5174,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:24">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -5181,9 +5200,9 @@
         <v>362</v>
       </c>
     </row>
-    <row r="178" spans="1:24">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B178">
         <v>2</v>
@@ -5207,9 +5226,9 @@
         <v>617</v>
       </c>
     </row>
-    <row r="179" spans="1:24">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B179">
         <v>3</v>
@@ -5233,9 +5252,9 @@
         <v>769</v>
       </c>
     </row>
-    <row r="180" spans="1:24">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B180">
         <v>4</v>
@@ -5259,9 +5278,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="181" spans="1:24">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B181">
         <v>5</v>
@@ -5285,9 +5304,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="182" spans="1:24">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -5311,9 +5330,9 @@
         <v>779</v>
       </c>
     </row>
-    <row r="183" spans="1:24">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B183">
         <v>2</v>
@@ -5337,9 +5356,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="184" spans="1:24">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B184">
         <v>3</v>
@@ -5363,9 +5382,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="185" spans="1:24">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B185">
         <v>4</v>
@@ -5389,9 +5408,9 @@
         <v>855</v>
       </c>
     </row>
-    <row r="186" spans="1:24">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B186">
         <v>5</v>
